--- a/excel/distribuidora-sol-del-valle-s-a-c_capacitaciones.xlsx
+++ b/excel/distribuidora-sol-del-valle-s-a-c_capacitaciones.xlsx
@@ -958,12 +958,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C001513040</t>
+          <t>C001674351</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C001513040 - ACOSTA FERNANDEZ MARCELINA ESTHER</t>
+          <t>C001674351 - YSIDRO SOCORRO ANELIDA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1048,12 +1048,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C001483227</t>
+          <t>C001669043</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C001483227 - VILLANUEVA HILARIO CYNTHIA YESENIA</t>
+          <t>C001669043 - ORBEGOSO MUÑOZ EMELDA ELIZABETH</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C001669043</t>
+          <t>C001513040</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C001669043 - ORBEGOSO MUÑOZ EMELDA ELIZABETH</t>
+          <t>C001513040 - ACOSTA FERNANDEZ MARCELINA ESTHER</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C001674351</t>
+          <t>C001483227</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C001674351 - YSIDRO SOCORRO ANELIDA</t>
+          <t>C001483227 - VILLANUEVA HILARIO CYNTHIA YESENIA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C001732698</t>
+          <t>C004197150</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C001732698 - TICLIAHUANCA REYNA MARILYN FLORENCIA</t>
+          <t>C004197150 - PONCE DOMINGUEZ MARIA PILAR</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C001733660</t>
+          <t>C004197221</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C001733660 - MIRANDA VARGAS MARIA YSABEL</t>
+          <t>C004197221 - VARGAS REYES ARCADIO MODESTO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C001760417</t>
+          <t>C004185437</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>C001760417 - BOCANEGRA HILARIO JHOORDYN AQUILES</t>
+          <t>C004185437 - ZAVALETA BAYLON PAOLA NOEMI</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1534,7 +1534,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C004185437</t>
+          <t>C004048840</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C004185437 - ZAVALETA BAYLON PAOLA NOEMI</t>
+          <t>C004048840 - CORTIJO NEYRA LUCERO DEL CIELO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C004197150</t>
+          <t>C001760417</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C004197150 - PONCE DOMINGUEZ MARIA PILAR</t>
+          <t>C001760417 - BOCANEGRA HILARIO JHOORDYN AQUILES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1714,7 +1714,7 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C004197221</t>
+          <t>C001732698</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C004197221 - VARGAS REYES ARCADIO MODESTO</t>
+          <t>C001732698 - TICLIAHUANCA REYNA MARILYN FLORENCIA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1858,12 +1858,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C004048840</t>
+          <t>C001733660</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C004048840 - CORTIJO NEYRA LUCERO DEL CIELO</t>
+          <t>C001733660 - MIRANDA VARGAS MARIA YSABEL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
@@ -1948,12 +1948,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C001392282</t>
+          <t>C001629991</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>C001392282 - POLO CRUZ JOSE SANTOS</t>
+          <t>C001629991 - AVILA RODRIGUEZ LADY ROSSELLI</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2038,12 +2038,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C001618305</t>
+          <t>C001563276</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C001618305 - MOGOLLON GARCIA JORGE LUIS</t>
+          <t>C001563276 - MENDEZ MENDEZ DEROMILDA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
@@ -2128,12 +2128,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C001563276</t>
+          <t>C001576999</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>C001563276 - MENDEZ MENDEZ DEROMILDA</t>
+          <t>C001576999 - TORRES LIZARRAGA GIANMARCO ANDRE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C001576999</t>
+          <t>C001618305</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C001576999 - TORRES LIZARRAGA GIANMARCO ANDRE</t>
+          <t>C001618305 - MOGOLLON GARCIA JORGE LUIS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C001629991</t>
+          <t>C001392282</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>C001629991 - AVILA RODRIGUEZ LADY ROSSELLI</t>
+          <t>C001392282 - POLO CRUZ JOSE SANTOS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C001740965</t>
+          <t>C001711464</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C001740965 - LAZARO NICASIO MARIBEL KARINA</t>
+          <t>C001711464 - DIONICIO HERNANDEZ MIRTA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2519,11 +2519,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -2562,7 +2558,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2582,12 +2578,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C001711464</t>
+          <t>C001740965</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>C001711464 - DIONICIO HERNANDEZ MIRTA</t>
+          <t>C001740965 - LAZARO NICASIO MARIBEL KARINA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2613,7 +2609,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C004190467</t>
+          <t>C004054693</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>C004190467 - GARCIA FAJARDO JAMPOOL JUNIOR</t>
+          <t>C004054693 - VASQUEZ VALDERRAMA SARA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C004199228</t>
+          <t>C004059726</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C004199228 - VALDIVIESO CABRERA VICTOR MELITON</t>
+          <t>C004059726 - GERONIMO PEREZ MARINO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C004054693</t>
+          <t>C004190467</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C004054693 - VASQUEZ VALDERRAMA SARA</t>
+          <t>C004190467 - GARCIA FAJARDO JAMPOOL JUNIOR</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -2942,12 +2942,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C004059726</t>
+          <t>C004199228</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C004059726 - GERONIMO PEREZ MARINO</t>
+          <t>C004199228 - VALDIVIESO CABRERA VICTOR MELITON</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C001734971</t>
+          <t>C001332822</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C001734971 - ALVARADO PRADO PEDRO NILTON</t>
+          <t>C001332822 - PINILLOS MARCELO KAREN TATIANA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C004170116</t>
+          <t>C001334859</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>C004170116 - REYES SALINAS MARTHA PEREGRINA</t>
+          <t>C001334859 - RODRIGUEZ VALDIVIESO LILIAN GLADYS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
@@ -3212,12 +3212,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C004170162</t>
+          <t>C004242893</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C004170162 - RODRIGUEZ RUIZ ADRIANA</t>
+          <t>C004242893 - MULTISERVICIOS GENERALES ZAVALETA S.A.C.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C001731317</t>
+          <t>C001687871</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>C001731317 - SANCHEZ MOZO MILI YOVANA</t>
+          <t>C001687871 - ROMERO PEREZ JESSICA MEDALY</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C001513253</t>
+          <t>C004170162</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>C001513253 - RODRIGUEZ VALDIVIESO YULI DEYSI</t>
+          <t>C004170162 - RODRIGUEZ RUIZ ADRIANA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C001712645</t>
+          <t>C001741503</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C001712645 - GUTIERREZ ROJAS ELVIN</t>
+          <t>C001741503 - FERREL DIESTRA ALEJANDRINA TEONILA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3572,12 +3572,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C001334859</t>
+          <t>C004170116</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C001334859 - RODRIGUEZ VALDIVIESO LILIAN GLADYS</t>
+          <t>C004170116 - REYES SALINAS MARTHA PEREGRINA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C001687871</t>
+          <t>C001731317</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C001687871 - ROMERO PEREZ JESSICA MEDALY</t>
+          <t>C001731317 - SANCHEZ MOZO MILI YOVANA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C001741503</t>
+          <t>C001732657</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C001741503 - FERREL DIESTRA ALEJANDRINA TEONILA</t>
+          <t>C001732657 - BACILIO SILVESTRE ROSA MAGALI</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C001732657</t>
+          <t>C001734971</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C001732657 - BACILIO SILVESTRE ROSA MAGALI</t>
+          <t>C001734971 - ALVARADO PRADO PEDRO NILTON</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C001332822</t>
+          <t>C001712645</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C001332822 - PINILLOS MARCELO KAREN TATIANA</t>
+          <t>C001712645 - GUTIERREZ ROJAS ELVIN</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C004242893</t>
+          <t>C001513253</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>C004242893 - MULTISERVICIOS GENERALES ZAVALETA S.A.C.</t>
+          <t>C001513253 - RODRIGUEZ VALDIVIESO YULI DEYSI</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C001682053</t>
+          <t>C001476009</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C001682053 - CONTRERAS MARQUINA IDAÑA MARDELID</t>
+          <t>C001476009 - JARA VILLAR ADOLFINA PETRONILA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C001476009</t>
+          <t>C001682053</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C001476009 - JARA VILLAR ADOLFINA PETRONILA</t>
+          <t>C001682053 - CONTRERAS MARQUINA IDAÑA MARDELID</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4652,12 +4652,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C001733600</t>
+          <t>C001731770</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>C001733600 - REYES CABRERA MELBER AGAPITO</t>
+          <t>C001731770 - BENITEZ RODRIGUEZ SEGUNDA FLORESTINA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4683,11 +4683,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
@@ -4746,12 +4742,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C001731770</t>
+          <t>C001733600</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C001731770 - BENITEZ RODRIGUEZ SEGUNDA FLORESTINA</t>
+          <t>C001733600 - REYES CABRERA MELBER AGAPITO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4777,7 +4773,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -6988,12 +6988,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C001578039</t>
+          <t>C001567587</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>C001578039 - AGUILAR URRUTIA ROSA KELLY</t>
+          <t>C001567587 - RUIZ MIÑANO ROSA FLOR</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7040,13 +7040,17 @@
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7078,12 +7082,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C001567587</t>
+          <t>C001578039</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C001567587 - RUIZ MIÑANO ROSA FLOR</t>
+          <t>C001578039 - AGUILAR URRUTIA ROSA KELLY</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7130,17 +7134,13 @@
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -7172,12 +7172,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C001127634</t>
+          <t>C001401840</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C001127634 - VIDAL GARCIA TERESA</t>
+          <t>C001401840 - VILLARREAL CONTRERAS ANACLETO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C001128962</t>
+          <t>C001324442</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>C001128962 - PAREDES HUAMAN SANTOS PETRONILA</t>
+          <t>C001324442 - GUTIERREZ DE OTINIANO SANTOS NILA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C001367258</t>
+          <t>C001127634</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>C001367258 - JOAQUIN SOBERON EDITH</t>
+          <t>C001127634 - VIDAL GARCIA TERESA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -7450,12 +7450,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C001324442</t>
+          <t>C001128962</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>C001324442 - GUTIERREZ DE OTINIANO SANTOS NILA</t>
+          <t>C001128962 - PAREDES HUAMAN SANTOS PETRONILA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C001401840</t>
+          <t>C001367258</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>C001401840 - VILLARREAL CONTRERAS ANACLETO</t>
+          <t>C001367258 - JOAQUIN SOBERON EDITH</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>C004196674</t>
+          <t>C004167851</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>C004196674 - ZEGARRA CALVA ZANDRA ELIZABET</t>
+          <t>C004167851 - VARAS HERNANDEZ HIMELINA ARANCEL</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -8550,12 +8550,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>C004197916</t>
+          <t>C004196674</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>C004197916 - RAMIREZ GOMEZ LUISA FERNANDA MARICEL</t>
+          <t>C004196674 - ZEGARRA CALVA ZANDRA ELIZABET</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8602,13 +8602,17 @@
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -8640,12 +8644,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C004167851</t>
+          <t>C004197916</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>C004167851 - VARAS HERNANDEZ HIMELINA ARANCEL</t>
+          <t>C004197916 - RAMIREZ GOMEZ LUISA FERNANDA MARICEL</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8692,17 +8696,13 @@
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
       <c r="V91" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -8734,12 +8734,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>C001733224</t>
+          <t>C001739071</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>C001733224 - BENITES LAZARO MARIA ESTHER</t>
+          <t>C001739071 - VEREAU ROSARIO SANTOS AIDEE</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8828,12 +8828,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C001737285</t>
+          <t>C001733224</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>C001737285 - GUTIERREZ AVILA ZULY JANETH</t>
+          <t>C001733224 - BENITES LAZARO MARIA ESTHER</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8880,13 +8880,17 @@
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -8918,12 +8922,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>C001739071</t>
+          <t>C001737285</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>C001739071 - VEREAU ROSARIO SANTOS AIDEE</t>
+          <t>C001737285 - GUTIERREZ AVILA ZULY JANETH</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8970,17 +8974,13 @@
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9196,12 +9196,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C001577408</t>
+          <t>C001324650</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>C001577408 - CABRERA LOYOLA DIANA MILY</t>
+          <t>C001324650 - ULLOA QUEZADA NATIVIDAD VILMA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9242,23 +9242,19 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9290,12 +9286,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C001324650</t>
+          <t>C001384058</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>C001324650 - ULLOA QUEZADA NATIVIDAD VILMA</t>
+          <t>C001384058 - RAMOS ROBLES YANINA BEATRIZ</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9380,12 +9376,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>C001384058</t>
+          <t>C001400565</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>C001384058 - RAMOS ROBLES YANINA BEATRIZ</t>
+          <t>C001400565 - QUISPE LOZANO SANTOS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -9426,19 +9422,23 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9470,12 +9470,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C001400565</t>
+          <t>C001577408</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>C001400565 - QUISPE LOZANO SANTOS</t>
+          <t>C001577408 - CABRERA LOYOLA DIANA MILY</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9527,12 +9527,12 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9842,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>C001740647</t>
+          <t>C001732191</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>C001740647 - SILVA DOMINGUEZ MIRIAM</t>
+          <t>C001732191 - ZAVALETA CASTAÑEDA OLGA ELOISA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9873,7 +9873,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
@@ -9936,12 +9940,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>C001732191</t>
+          <t>C001740647</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>C001732191 - ZAVALETA CASTAÑEDA OLGA ELOISA</t>
+          <t>C001740647 - SILVA DOMINGUEZ MIRIAM</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -9967,11 +9971,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
@@ -10197,7 +10197,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>HUAMACHUCO</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -10222,17 +10222,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>C001490935</t>
+          <t>C001285138</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>C001490935 - BERROCAL NAPAN JESSICA SOLEDAD</t>
+          <t>C001285138 - POLO ARANDA DIRSON PAUL</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -10256,9 +10256,21 @@
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr">
         <is>
@@ -10275,7 +10287,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>HUAMACHUCO</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10290,7 +10302,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10300,17 +10312,17 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>C001285138</t>
+          <t>C001490935</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>C001285138 - POLO ARANDA DIRSON PAUL</t>
+          <t>C001490935 - BERROCAL NAPAN JESSICA SOLEDAD</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
@@ -10323,7 +10335,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -10334,21 +10346,9 @@
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HUAMACHUCO</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>C001455878</t>
+          <t>C001285463</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>C001455878 - JULCA NEYRA LUIS JAIME</t>
+          <t>C001285463 - DE LA CRUZ ROMAN CLARA</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10536,17 +10536,13 @@
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr"/>
       <c r="V111" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -10647,7 +10643,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>HUAMACHUCO</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10672,12 +10668,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>C001285463</t>
+          <t>C001455878</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>C001285463 - DE LA CRUZ ROMAN CLARA</t>
+          <t>C001455878 - JULCA NEYRA LUIS JAIME</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10724,13 +10720,17 @@
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U113" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11040,12 +11040,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>C004183620</t>
+          <t>C004060020</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>C004183620 - RODRIGUEZ TORRES FLORA ARCILA</t>
+          <t>C004060020 - GARCIA AURORA SANTOS GILBERTA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -11134,12 +11134,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>C004167730</t>
+          <t>C004183620</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>C004167730 - LIZARRAGA BACA FIDELIA AXILDA</t>
+          <t>C004183620 - RODRIGUEZ TORRES FLORA ARCILA</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>C004060020</t>
+          <t>C004167730</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>C004060020 - GARCIA AURORA SANTOS GILBERTA</t>
+          <t>C004167730 - LIZARRAGA BACA FIDELIA AXILDA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -12048,7 +12048,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -12058,17 +12058,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>C004167428</t>
+          <t>C004060767</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>C004167428 - RODRIGUEZ CORVERA JAYER LUIS</t>
+          <t>C004060767 - VEGA ARGOMEDO LUIS ALBERTO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -12092,9 +12092,21 @@
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr">
         <is>
@@ -12103,12 +12115,12 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12142,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12140,17 +12152,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>C004060767</t>
+          <t>C004167428</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>C004060767 - VEGA ARGOMEDO LUIS ALBERTO</t>
+          <t>C004167428 - RODRIGUEZ CORVERA JAYER LUIS</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
@@ -12163,7 +12175,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -12174,21 +12186,9 @@
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="R129" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr"/>
       <c r="T129" t="inlineStr">
         <is>
@@ -12197,12 +12197,12 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>

--- a/excel/distribuidora-sol-del-valle-s-a-c_capacitaciones.xlsx
+++ b/excel/distribuidora-sol-del-valle-s-a-c_capacitaciones.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Capacitaciones'!$A$1:$V$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Capacitaciones'!$A$1:$V$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V144"/>
+  <dimension ref="A1:V164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -598,12 +598,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C001331142</t>
+          <t>C001345662</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C001331142 - FERREL LOPEZ DE LAZARO TOMASA TERESA</t>
+          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -650,13 +650,17 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -668,7 +672,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -688,12 +692,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C001331144</t>
+          <t>C001405781</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C001331144 - INFANTES CHACON YOLANDA MARINA</t>
+          <t>C001405781 - ARAUJO AGUILAR KELLER MARJORIE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -702,7 +706,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -778,12 +782,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C001331147</t>
+          <t>C001396749</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C001331147 - PEREZ ESQUIVEL ANITA RAQUEL</t>
+          <t>C001396749 - FLORES ROSALES JUANITA JULIA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -792,7 +796,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -868,12 +872,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C001331346</t>
+          <t>C001398311</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C001331346 - LOPEZ POLO MARIA FLORENCIA</t>
+          <t>C001398311 - ARAUJO QUILICHE ANA CLAIRE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -882,7 +886,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -914,7 +918,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S5" t="inlineStr"/>
@@ -958,12 +962,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C001674351</t>
+          <t>C001612867</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C001674351 - YSIDRO SOCORRO ANELIDA</t>
+          <t>C001612867 - DIAZ RAFAEL ERIKA MARIVI</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -972,7 +976,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1004,7 +1008,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más capacitación</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -1028,7 +1032,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1048,12 +1052,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C001669043</t>
+          <t>C001767433</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C001669043 - ORBEGOSO MUÑOZ EMELDA ELIZABETH</t>
+          <t>C001767433 - RODRIGUEZ BEJARANO SEGUNDO EUSEBIO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1062,7 +1066,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1094,7 +1098,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1138,12 +1142,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C001513040</t>
+          <t>C001626791</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C001513040 - ACOSTA FERNANDEZ MARCELINA ESTHER</t>
+          <t>C001626791 - RAMIREZ BERNABE JEAN POOL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1152,7 +1156,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1184,7 +1188,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1228,12 +1232,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C001483227</t>
+          <t>C004192601</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C001483227 - VILLANUEVA HILARIO CYNTHIA YESENIA</t>
+          <t>C004192601 - CARLOS RODRIGUEZ MARLENI LUZVENI</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1242,7 +1246,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1274,19 +1278,23 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1326,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C004197150</t>
+          <t>C004189303</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C004197150 - PONCE DOMINGUEZ MARIA PILAR</t>
+          <t>C004189303 - RODRIGUEZ AVALOS GLORIA HAYDEE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1332,7 +1340,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1408,12 +1416,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C004197221</t>
+          <t>C004050172</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C004197221 - VARGAS REYES ARCADIO MODESTO</t>
+          <t>C004050172 - RODRIGUEZ VASQUEZ ROSARIO ANGELICA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1422,7 +1430,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1454,7 +1462,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -1498,12 +1506,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C004185437</t>
+          <t>C004167425</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>C004185437 - ZAVALETA BAYLON PAOLA NOEMI</t>
+          <t>C004167425 - FELIPE BAZAN DE ROJAS BETTY MARUJA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1512,7 +1520,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1544,19 +1552,23 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1600,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C004048840</t>
+          <t>C004242198</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C004048840 - CORTIJO NEYRA LUCERO DEL CIELO</t>
+          <t>C004242198 - ALFARO FLORES MILAGROS AMPARO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1602,7 +1614,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1624,7 +1636,7 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1634,19 +1646,23 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1694,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C001760417</t>
+          <t>C001167763</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C001760417 - BOCANEGRA HILARIO JHOORDYN AQUILES</t>
+          <t>C001167763 - MORI BARTOLOME ANA ISABEL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1692,7 +1708,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1714,7 +1730,7 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1768,12 +1784,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C001732698</t>
+          <t>C001364499</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C001732698 - TICLIAHUANCA REYNA MARILYN FLORENCIA</t>
+          <t>C001364499 - BURGOS DE QUISPE OLGA DALILA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1782,7 +1798,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1858,12 +1874,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C001733660</t>
+          <t>C001559213</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C001733660 - MIRANDA VARGAS MARIA YSABEL</t>
+          <t>C001559213 - RUIZ ESPINOZA DELIA ISABEL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1872,7 +1888,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1904,19 +1920,23 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1948,12 +1968,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C001629991</t>
+          <t>C001676127</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>C001629991 - AVILA RODRIGUEZ LADY ROSSELLI</t>
+          <t>C001676127 - ESCOVEDO AREDO ANITA ANDREA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1962,7 +1982,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1989,7 +2009,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2038,12 +2058,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C001563276</t>
+          <t>C004190849</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C001563276 - MENDEZ MENDEZ DEROMILDA</t>
+          <t>C004190849 - VALVERDE ULLOA SANTOS AGUSTINA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2052,7 +2072,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2069,7 +2089,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2108,7 +2132,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2128,12 +2152,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C001576999</t>
+          <t>C001409233</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>C001576999 - TORRES LIZARRAGA GIANMARCO ANDRE</t>
+          <t>C001409233 - VERA CRUZ NATHALY SAMANTHA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2142,7 +2166,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2174,7 +2198,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
@@ -2198,7 +2222,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2218,12 +2242,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C001618305</t>
+          <t>C001572723</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C001618305 - MOGOLLON GARCIA JORGE LUIS</t>
+          <t>C001572723 - LIÑAN TORRES ASUNCION ROSMERY</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2232,7 +2256,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2264,19 +2288,23 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -2308,12 +2336,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C001392282</t>
+          <t>C001562946</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>C001392282 - POLO CRUZ JOSE SANTOS</t>
+          <t>C001562946 - CUSTODIO BRICEÑO LILY MARILU</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2322,7 +2350,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2354,7 +2382,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
@@ -2398,12 +2426,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C001405766</t>
+          <t>C001331142</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>C001405766 - CASTAÑEDA CASTAÑEDA EMILIO</t>
+          <t>C001331142 - FERREL LOPEZ DE LAZARO TOMASA TERESA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2412,7 +2440,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2439,7 +2467,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2450,13 +2478,17 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -2488,12 +2520,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C001711464</t>
+          <t>C001331144</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>C001711464 - DIONICIO HERNANDEZ MIRTA</t>
+          <t>C001331144 - INFANTES CHACON YOLANDA MARINA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2502,7 +2534,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2558,7 +2590,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2578,12 +2610,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C001740965</t>
+          <t>C001331147</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>C001740965 - LAZARO NICASIO MARIBEL KARINA</t>
+          <t>C001331147 - PEREZ ESQUIVEL ANITA RAQUEL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2592,7 +2624,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2609,11 +2641,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -2634,13 +2662,17 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -2672,12 +2704,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C004054693</t>
+          <t>C001331346</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>C004054693 - VASQUEZ VALDERRAMA SARA</t>
+          <t>C001331346 - LOPEZ POLO MARIA FLORENCIA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2686,7 +2718,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2718,19 +2750,23 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -2762,12 +2798,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C004059726</t>
+          <t>C001674351</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C004059726 - GERONIMO PEREZ MARINO</t>
+          <t>C001674351 - YSIDRO SOCORRO ANELIDA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2776,7 +2812,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -2832,7 +2868,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2852,12 +2888,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C004190467</t>
+          <t>C001669043</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C004190467 - GARCIA FAJARDO JAMPOOL JUNIOR</t>
+          <t>C001669043 - ORBEGOSO MUÑOZ EMELDA ELIZABETH</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2866,7 +2902,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2898,7 +2934,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S27" t="inlineStr"/>
@@ -2942,12 +2978,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C004199228</t>
+          <t>C001483227</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C004199228 - VALDIVIESO CABRERA VICTOR MELITON</t>
+          <t>C001483227 - VILLANUEVA HILARIO CYNTHIA YESENIA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2956,7 +2992,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -2988,7 +3024,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -3032,12 +3068,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C001332822</t>
+          <t>C001513040</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C001332822 - PINILLOS MARCELO KAREN TATIANA</t>
+          <t>C001513040 - ACOSTA FERNANDEZ MARCELINA ESTHER</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3046,7 +3082,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -3122,12 +3158,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>C001334859</t>
+          <t>C004197150</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>C001334859 - RODRIGUEZ VALDIVIESO LILIAN GLADYS</t>
+          <t>C004197150 - PONCE DOMINGUEZ MARIA PILAR</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3136,7 +3172,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -3168,19 +3204,23 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Más productos disponibles</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3212,12 +3252,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>C004242893</t>
+          <t>C004197221</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>C004242893 - MULTISERVICIOS GENERALES ZAVALETA S.A.C.</t>
+          <t>C004197221 - VARGAS REYES ARCADIO MODESTO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3226,7 +3266,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -3253,12 +3293,12 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
@@ -3302,12 +3342,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>C001687871</t>
+          <t>C004185437</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>C001687871 - ROMERO PEREZ JESSICA MEDALY</t>
+          <t>C004185437 - ZAVALETA BAYLON PAOLA NOEMI</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3316,7 +3356,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -3348,19 +3388,23 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3392,12 +3436,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>C004170162</t>
+          <t>C001732698</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>C004170162 - RODRIGUEZ RUIZ ADRIANA</t>
+          <t>C001732698 - TICLIAHUANCA REYNA MARILYN FLORENCIA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3406,7 +3450,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3444,13 +3488,17 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3482,12 +3530,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C001741503</t>
+          <t>C001733660</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>C001741503 - FERREL DIESTRA ALEJANDRINA TEONILA</t>
+          <t>C001733660 - MIRANDA VARGAS MARIA YSABEL</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3496,7 +3544,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -3523,12 +3571,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -3572,12 +3620,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C004170116</t>
+          <t>C001760417</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C004170116 - REYES SALINAS MARTHA PEREGRINA</t>
+          <t>C001760417 - BOCANEGRA HILARIO JHOORDYN AQUILES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3586,7 +3634,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -3608,7 +3656,7 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3642,7 +3690,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3662,12 +3710,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C001731317</t>
+          <t>C004048840</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C001731317 - SANCHEZ MOZO MILI YOVANA</t>
+          <t>C004048840 - CORTIJO NEYRA LUCERO DEL CIELO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3676,7 +3724,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -3708,19 +3756,23 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3752,12 +3804,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C001732657</t>
+          <t>C004199228</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C001732657 - BACILIO SILVESTRE ROSA MAGALI</t>
+          <t>C004199228 - VALDIVIESO CABRERA VICTOR MELITON</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3766,7 +3818,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3804,13 +3856,17 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3842,12 +3898,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C001734971</t>
+          <t>C004190467</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C001734971 - ALVARADO PRADO PEDRO NILTON</t>
+          <t>C004190467 - GARCIA FAJARDO JAMPOOL JUNIOR</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3856,7 +3912,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -3888,19 +3944,23 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3932,12 +3992,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C001712645</t>
+          <t>C001711464</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C001712645 - GUTIERREZ ROJAS ELVIN</t>
+          <t>C001711464 - DIONICIO HERNANDEZ MIRTA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3946,7 +4006,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3984,13 +4044,17 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4066,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4022,12 +4086,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C001513253</t>
+          <t>C001740965</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>C001513253 - RODRIGUEZ VALDIVIESO YULI DEYSI</t>
+          <t>C001740965 - LAZARO NICASIO MARIBEL KARINA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4036,7 +4100,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -4053,7 +4117,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -4112,12 +4180,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C001476009</t>
+          <t>C004054693</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C001476009 - JARA VILLAR ADOLFINA PETRONILA</t>
+          <t>C004054693 - VASQUEZ VALDERRAMA SARA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4126,7 +4194,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -4164,13 +4232,17 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4202,12 +4274,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C001667496</t>
+          <t>C004059726</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>C001667496 - RODRIGUEZ AGUILAR FLORA</t>
+          <t>C004059726 - GERONIMO PEREZ MARINO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4216,7 +4288,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -4292,12 +4364,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C001529571</t>
+          <t>C001629991</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>C001529571 - CRUZADO PULIDO LORENA LICETH</t>
+          <t>C001629991 - AVILA RODRIGUEZ LADY ROSSELLI</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4306,7 +4378,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -4333,7 +4405,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4344,13 +4416,17 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4438,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4382,12 +4458,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C001682053</t>
+          <t>C001618305</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C001682053 - CONTRERAS MARQUINA IDAÑA MARDELID</t>
+          <t>C001618305 - MOGOLLON GARCIA JORGE LUIS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4396,7 +4472,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -4428,7 +4504,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S44" t="inlineStr"/>
@@ -4452,7 +4528,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4472,12 +4548,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C001750147</t>
+          <t>C001563276</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>C001750147 - JARA GUEVARA KARINE YUDIT</t>
+          <t>C001563276 - MENDEZ MENDEZ DEROMILDA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4486,7 +4562,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -4518,19 +4594,23 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4562,12 +4642,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C001737180</t>
+          <t>C001576999</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>C001737180 - CASTILLO RAMIREZ EYLEEN JULICSA</t>
+          <t>C001576999 - TORRES LIZARRAGA GIANMARCO ANDRE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4576,7 +4656,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -4608,19 +4688,23 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -4652,12 +4736,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C001731770</t>
+          <t>C001405766</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>C001731770 - BENITEZ RODRIGUEZ SEGUNDA FLORESTINA</t>
+          <t>C001405766 - CASTAÑEDA CASTAÑEDA EMILIO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4666,7 +4750,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -4693,7 +4777,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4742,12 +4826,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C001733600</t>
+          <t>C001392282</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C001733600 - REYES CABRERA MELBER AGAPITO</t>
+          <t>C001392282 - POLO CRUZ JOSE SANTOS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4756,7 +4840,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -4773,11 +4857,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -4836,12 +4916,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C004047558</t>
+          <t>C001334859</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>C004047558 - TRUJILLO ROJAS WILDER DANIEL</t>
+          <t>C001334859 - RODRIGUEZ VALDIVIESO LILIAN GLADYS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4850,7 +4930,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -4882,19 +4962,23 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más productos disponibles</t>
         </is>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4990,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4926,12 +5010,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C004182389</t>
+          <t>C001731317</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>C004182389 - ZAVALETA ÑIQUE MARIA ELENA</t>
+          <t>C001731317 - SANCHEZ MOZO MILI YOVANA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4940,7 +5024,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -5016,12 +5100,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C001371461</t>
+          <t>C001734971</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>C001371461 - BAZAN MOYA LESLIE JULIANA</t>
+          <t>C001734971 - ALVARADO PRADO PEDRO NILTON</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5030,7 +5114,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -5106,12 +5190,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C001119171</t>
+          <t>C001513253</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C001119171 - ROMERO DE CIPRA AMELIA GOSBINDA</t>
+          <t>C001513253 - RODRIGUEZ VALDIVIESO YULI DEYSI</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5120,7 +5204,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -5196,12 +5280,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C001125965</t>
+          <t>C001712645</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>C001125965 - PAISIG ALVA ANA MARIA</t>
+          <t>C001712645 - GUTIERREZ ROJAS ELVIN</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5210,7 +5294,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -5286,12 +5370,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C001533964</t>
+          <t>C004170116</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C001533964 - LOPEZ CASANOVA MERCI NERI</t>
+          <t>C004170116 - REYES SALINAS MARTHA PEREGRINA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5300,7 +5384,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -5332,7 +5416,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S54" t="inlineStr"/>
@@ -5376,12 +5460,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C001513618</t>
+          <t>C001741503</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>C001513618 - MERCEDES LEDESMA VICTOR ADOLFO</t>
+          <t>C001741503 - FERREL DIESTRA ALEJANDRINA TEONILA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5390,7 +5474,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -5417,12 +5501,12 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S55" t="inlineStr"/>
@@ -5466,12 +5550,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C004048781</t>
+          <t>C001687871</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>C004048781 - ESQUIVEL PICHEN ANTOLINA ROSALIA</t>
+          <t>C001687871 - ROMERO PEREZ JESSICA MEDALY</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5480,7 +5564,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -5512,7 +5596,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
@@ -5556,12 +5640,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C004061920</t>
+          <t>C001732657</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>C004061920 - CARBAJAL PRETEL DANTE AMIN</t>
+          <t>C001732657 - BACILIO SILVESTRE ROSA MAGALI</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5570,7 +5654,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -5646,12 +5730,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C004173978</t>
+          <t>C001332822</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C004173978 - ROMERO BUENO MARIA PILAR</t>
+          <t>C001332822 - PINILLOS MARCELO KAREN TATIANA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5660,7 +5744,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -5692,19 +5776,23 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5824,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C001706255</t>
+          <t>C004242893</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>C001706255 - CRUZ GONZALES HELGA EVELYN</t>
+          <t>C004242893 - MULTISERVICIOS GENERALES ZAVALETA S.A.C.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5750,7 +5838,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -5777,7 +5865,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5826,12 +5914,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C001554836</t>
+          <t>C004170162</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C001554836 - MALCA CERCADO SEGUNDO RICARDO</t>
+          <t>C004170162 - RODRIGUEZ RUIZ ADRIANA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5840,7 +5928,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -5872,7 +5960,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S60" t="inlineStr"/>
@@ -5916,12 +6004,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C001499810</t>
+          <t>C001682053</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C001499810 - CASTILLO NARRO DE BRAVO MAGALI ROSELI</t>
+          <t>C001682053 - CONTRERAS MARQUINA IDAÑA MARDELID</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5930,7 +6018,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -5968,13 +6056,17 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6006,12 +6098,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C001502148</t>
+          <t>C001667496</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>C001502148 - MINCHOLA DIONICIO MAYRA MILEYDI</t>
+          <t>C001667496 - RODRIGUEZ AGUILAR FLORA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6020,7 +6112,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -6058,13 +6150,17 @@
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6182,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6096,21 +6192,21 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C001324430</t>
+          <t>C001529571</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>C001324430 - MORILLAS CABALLERO SANTOS CATALINA</t>
+          <t>C001529571 - CRUZADO PULIDO LORENA LICETH</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -6119,7 +6215,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6130,9 +6226,21 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr">
         <is>
@@ -6174,12 +6282,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C001179289</t>
+          <t>C001476009</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>C001179289 - ARMAS DE TOCTO MARIA CONVERCION</t>
+          <t>C001476009 - JARA VILLAR ADOLFINA PETRONILA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6188,7 +6296,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -6220,19 +6328,23 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6264,12 +6376,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C001179290</t>
+          <t>C001733600</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C001179290 - CHIZA GUEVARA FLOR ANGELICA</t>
+          <t>C001733600 - REYES CABRERA MELBER AGAPITO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6278,7 +6390,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -6295,7 +6407,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -6316,13 +6432,17 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6354,12 +6474,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C001115972</t>
+          <t>C001731770</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>C001115972 - BENITES MAURICIO ROSA INES</t>
+          <t>C001731770 - BENITEZ RODRIGUEZ SEGUNDA FLORESTINA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -6368,7 +6488,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -6406,13 +6526,17 @@
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6444,12 +6568,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C001117422</t>
+          <t>C001737180</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>C001117422 - LIZARRAGA GUTIERREZ ANTERO DANIEL</t>
+          <t>C001737180 - CASTILLO RAMIREZ EYLEEN JULICSA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6458,7 +6582,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -6514,7 +6638,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6534,12 +6658,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>C001125639</t>
+          <t>C001750147</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>C001125639 - QUIROZ MARIN JUAN EDGARDO</t>
+          <t>C001750147 - JARA GUEVARA KARINE YUDIT</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6548,7 +6672,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -6580,7 +6704,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S68" t="inlineStr"/>
@@ -6624,12 +6748,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>C001125879</t>
+          <t>C004047558</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>C001125879 - GONZALES CHUQUIMANGO ANITA NIEVES</t>
+          <t>C004047558 - TRUJILLO ROJAS WILDER DANIEL</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6638,7 +6762,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -6670,19 +6794,23 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6714,12 +6842,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>C004166670</t>
+          <t>C004182389</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>C004166670 - RODRIGUEZ RODRIGUEZ GABBY ROSSI</t>
+          <t>C004182389 - ZAVALETA ÑIQUE MARIA ELENA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6728,7 +6856,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -6808,12 +6936,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>C004234804</t>
+          <t>C001371461</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>C004234804 - TORRES RAMOS MARIA YANE</t>
+          <t>C001371461 - BAZAN MOYA LESLIE JULIANA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6822,7 +6950,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -6860,13 +6988,17 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6898,12 +7030,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>C004214056</t>
+          <t>C001119171</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>C004214056 - AMAYA CAMACHO CARLOS ANTONIO</t>
+          <t>C001119171 - ROMERO DE CIPRA AMELIA GOSBINDA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6912,7 +7044,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -6988,12 +7120,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>C001567587</t>
+          <t>C001125965</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>C001567587 - RUIZ MIÑANO ROSA FLOR</t>
+          <t>C001125965 - PAISIG ALVA ANA MARIA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7002,7 +7134,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -7082,12 +7214,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>C001578039</t>
+          <t>C001513618</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>C001578039 - AGUILAR URRUTIA ROSA KELLY</t>
+          <t>C001513618 - MERCEDES LEDESMA VICTOR ADOLFO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -7096,7 +7228,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -7128,7 +7260,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S74" t="inlineStr"/>
@@ -7172,12 +7304,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>C001401840</t>
+          <t>C001533964</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>C001401840 - VILLARREAL CONTRERAS ANACLETO</t>
+          <t>C001533964 - LOPEZ CASANOVA MERCI NERI</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7186,7 +7318,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -7218,7 +7350,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S75" t="inlineStr"/>
@@ -7266,12 +7398,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>C001324442</t>
+          <t>C004048781</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>C001324442 - GUTIERREZ DE OTINIANO SANTOS NILA</t>
+          <t>C004048781 - ESQUIVEL PICHEN ANTOLINA ROSALIA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -7280,7 +7412,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -7312,19 +7444,23 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -7356,12 +7492,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>C001127634</t>
+          <t>C004061920</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>C001127634 - VIDAL GARCIA TERESA</t>
+          <t>C004061920 - CARBAJAL PRETEL DANTE AMIN</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7370,7 +7506,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -7450,12 +7586,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>C001128962</t>
+          <t>C004173978</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>C001128962 - PAREDES HUAMAN SANTOS PETRONILA</t>
+          <t>C004173978 - ROMERO BUENO MARIA PILAR</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -7464,7 +7600,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -7496,19 +7632,23 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7540,12 +7680,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>C001367258</t>
+          <t>C001706255</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>C001367258 - JOAQUIN SOBERON EDITH</t>
+          <t>C001706255 - CRUZ GONZALES HELGA EVELYN</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7554,7 +7694,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -7581,7 +7721,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -7597,12 +7737,12 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -7634,12 +7774,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>C004241687</t>
+          <t>C001554836</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>C004241687 - MIGUEL BARRIOS ROSMERY</t>
+          <t>C001554836 - MALCA CERCADO SEGUNDO RICARDO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7648,7 +7788,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -7686,13 +7826,17 @@
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -7724,12 +7868,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C004168393</t>
+          <t>C001115972</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>C004168393 - RODRIGUEZ VEGA GLORIA</t>
+          <t>C001115972 - BENITES MAURICIO ROSA INES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7738,7 +7882,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -7770,19 +7914,23 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -7814,12 +7962,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>C004047605</t>
+          <t>C001117422</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>C004047605 - VALVERDE VARGAS DE DAGA ROSITA INES</t>
+          <t>C001117422 - LIZARRAGA GUTIERREZ ANTERO DANIEL</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -7828,7 +7976,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -7866,13 +8014,17 @@
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7904,12 +8056,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>C004050163</t>
+          <t>C001125639</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>C004050163 - GARCIA CASTRO ROSMERY ELIZABETH</t>
+          <t>C001125639 - QUIROZ MARIN JUAN EDGARDO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -7918,7 +8070,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -7950,19 +8102,23 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -7994,12 +8150,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>C001736497</t>
+          <t>C001125879</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>C001736497 - VILLENA BECERRA SHUSEY ESTEFANY</t>
+          <t>C001125879 - GONZALES CHUQUIMANGO ANITA NIEVES</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -8008,7 +8164,7 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -8040,23 +8196,19 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -8088,12 +8240,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>C001676187</t>
+          <t>C001499810</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>C001676187 - GOICOCHEA AREVALO JUAN JENINFER</t>
+          <t>C001499810 - CASTILLO NARRO DE BRAVO MAGALI ROSELI</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8102,7 +8254,7 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -8140,13 +8292,17 @@
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8334,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>C001711123</t>
+          <t>C001502148</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>C001711123 - LAIZA ZAVALETA ESTRELLITA NELLY</t>
+          <t>C001502148 - MINCHOLA DIONICIO MAYRA MILEYDI</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8192,7 +8348,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -8230,13 +8386,17 @@
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -8258,7 +8418,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -8268,21 +8428,21 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>C001612754</t>
+          <t>C001324430</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>C001612754 - GAVIDIA VARGAS ELIZABETH AURORA</t>
+          <t>C001324430 - MORILLAS CABALLERO SANTOS CATALINA</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -8291,7 +8451,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -8302,35 +8462,19 @@
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -8362,12 +8506,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>C001413893</t>
+          <t>C001179289</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>C001413893 - MINCHOLA VELARDE ERCILA YESENIA</t>
+          <t>C001179289 - ARMAS DE TOCTO MARIA CONVERCION</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -8376,7 +8520,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -8408,7 +8552,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S88" t="inlineStr"/>
@@ -8419,12 +8563,12 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -8456,12 +8600,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>C004167851</t>
+          <t>C001179290</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>C004167851 - VARAS HERNANDEZ HIMELINA ARANCEL</t>
+          <t>C001179290 - CHIZA GUEVARA FLOR ANGELICA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -8470,7 +8614,7 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -8513,12 +8657,12 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -8550,12 +8694,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>C004196674</t>
+          <t>C004214056</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>C004196674 - ZEGARRA CALVA ZANDRA ELIZABET</t>
+          <t>C004214056 - AMAYA CAMACHO CARLOS ANTONIO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -8564,7 +8708,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -8644,12 +8788,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>C004197916</t>
+          <t>C004234804</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>C004197916 - RAMIREZ GOMEZ LUISA FERNANDA MARICEL</t>
+          <t>C004234804 - TORRES RAMOS MARIA YANE</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8658,7 +8802,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -8696,13 +8840,17 @@
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -8734,12 +8882,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>C001739071</t>
+          <t>C001127634</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>C001739071 - VEREAU ROSARIO SANTOS AIDEE</t>
+          <t>C001127634 - VIDAL GARCIA TERESA</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8748,7 +8896,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -8828,12 +8976,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C001733224</t>
+          <t>C001128962</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>C001733224 - BENITES LAZARO MARIA ESTHER</t>
+          <t>C001128962 - PAREDES HUAMAN SANTOS PETRONILA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -8842,7 +8990,7 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -8885,12 +9033,12 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -8922,12 +9070,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>C001737285</t>
+          <t>C004166670</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>C001737285 - GUTIERREZ AVILA ZULY JANETH</t>
+          <t>C004166670 - RODRIGUEZ RODRIGUEZ GABBY ROSSI</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -8936,7 +9084,7 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -8974,13 +9122,17 @@
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9012,12 +9164,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>C001759977</t>
+          <t>C001578039</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>C001759977 - ARENAS VARGAS NAOMI STEPHANY</t>
+          <t>C001578039 - AGUILAR URRUTIA ROSA KELLY</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9026,7 +9178,7 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -9064,13 +9216,17 @@
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -9102,12 +9258,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>C004183506</t>
+          <t>C001567587</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>C004183506 - PAREDES VASQUEZ ISABEL NOLBERTA</t>
+          <t>C001567587 - RUIZ MIÑANO ROSA FLOR</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9116,7 +9272,7 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -9143,7 +9299,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -9196,12 +9352,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C001324650</t>
+          <t>C001401840</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>C001324650 - ULLOA QUEZADA NATIVIDAD VILMA</t>
+          <t>C001401840 - VILLARREAL CONTRERAS ANACLETO</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9210,7 +9366,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -9242,19 +9398,23 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9286,12 +9446,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C001384058</t>
+          <t>C001367258</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>C001384058 - RAMOS ROBLES YANINA BEATRIZ</t>
+          <t>C001367258 - JOAQUIN SOBERON EDITH</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9300,7 +9460,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -9327,24 +9487,28 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9540,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>C001400565</t>
+          <t>C001324442</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>C001400565 - QUISPE LOZANO SANTOS</t>
+          <t>C001324442 - GUTIERREZ DE OTINIANO SANTOS NILA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -9390,7 +9554,7 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -9428,17 +9592,13 @@
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
       <c r="V99" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9470,12 +9630,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>C001577408</t>
+          <t>C004241687</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>C001577408 - CABRERA LOYOLA DIANA MILY</t>
+          <t>C004241687 - MIGUEL BARRIOS ROSMERY</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9484,7 +9644,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -9522,17 +9682,13 @@
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9564,12 +9720,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>C004168628</t>
+          <t>C004168393</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>C004168628 - SILVA DOMINGUEZ HERNAN</t>
+          <t>C004168393 - RODRIGUEZ VEGA GLORIA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9578,7 +9734,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -9610,19 +9766,23 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9654,12 +9814,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>C004169388</t>
+          <t>C004047605</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>C004169388 - JULCA REYES MARIA ROSMERIA</t>
+          <t>C004047605 - VALVERDE VARGAS DE DAGA ROSITA INES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9668,7 +9828,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -9711,12 +9871,12 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9748,12 +9908,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>C004171449</t>
+          <t>C004050163</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>C004171449 - CRUZ QUISPE ETHEL MELIZA</t>
+          <t>C004050163 - GARCIA CASTRO ROSMERY ELIZABETH</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -9762,7 +9922,7 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -9794,23 +9954,19 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9998,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>C001732191</t>
+          <t>C001676187</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>C001732191 - ZAVALETA CASTAÑEDA OLGA ELOISA</t>
+          <t>C001676187 - GOICOCHEA AREVALO JUAN JENINFER</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -9856,7 +10012,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -9873,11 +10029,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
@@ -9940,12 +10092,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>C001740647</t>
+          <t>C001736497</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>C001740647 - SILVA DOMINGUEZ MIRIAM</t>
+          <t>C001736497 - VILLENA BECERRA SHUSEY ESTEFANY</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -9954,7 +10106,7 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -10034,12 +10186,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>C001645160</t>
+          <t>C001711123</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>C001645160 - GOMEZ UGARTE ROSA</t>
+          <t>C001711123 - LAIZA ZAVALETA ESTRELLITA NELLY</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -10048,7 +10200,7 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -10128,12 +10280,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>C004224142</t>
+          <t>C001612754</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>C004224142 - RAMIREZ FLORES ALEJANDRO DANIEL</t>
+          <t>C001612754 - GAVIDIA VARGAS ELIZABETH AURORA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -10142,7 +10294,7 @@
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -10222,12 +10374,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>C001285138</t>
+          <t>C001413893</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>C001285138 - POLO ARANDA DIRSON PAUL</t>
+          <t>C001413893 - MINCHOLA VELARDE ERCILA YESENIA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -10236,7 +10388,7 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -10274,20 +10426,24 @@
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>HUAMACHUCO</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10302,7 +10458,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Prefiere pedir con su vendedor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10312,21 +10468,21 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>C001490935</t>
+          <t>C004196674</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>C001490935 - BERROCAL NAPAN JESSICA SOLEDAD</t>
+          <t>C004196674 - ZEGARRA CALVA ZANDRA ELIZABET</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -10335,7 +10491,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -10346,19 +10502,35 @@
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10390,12 +10562,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>C001521872</t>
+          <t>C004197916</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>C001521872 - GRAOS BRICENO FREDY RONALD</t>
+          <t>C004197916 - RAMIREZ GOMEZ LUISA FERNANDA MARICEL</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -10404,7 +10576,7 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -10484,12 +10656,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>C001285463</t>
+          <t>C004167851</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>C001285463 - DE LA CRUZ ROMAN CLARA</t>
+          <t>C004167851 - VARAS HERNANDEZ HIMELINA ARANCEL</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -10498,7 +10670,7 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -10536,13 +10708,17 @@
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -10574,12 +10750,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>C001370989</t>
+          <t>C001739071</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>C001370989 - ESQUIVEL ENRIQUEZ TEODOLINDA</t>
+          <t>C001739071 - VEREAU ROSARIO SANTOS AIDEE</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -10588,7 +10764,7 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -10615,7 +10791,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
@@ -10643,7 +10819,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>HUAMACHUCO</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10668,12 +10844,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>C001455878</t>
+          <t>C001733224</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>C001455878 - JULCA NEYRA LUIS JAIME</t>
+          <t>C001733224 - BENITES LAZARO MARIA ESTHER</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -10682,7 +10858,7 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -10762,12 +10938,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>C001761062</t>
+          <t>C001737285</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>C001761062 - CERNA PRIETO MARTINA</t>
+          <t>C001737285 - GUTIERREZ AVILA ZULY JANETH</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -10776,7 +10952,7 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -10856,12 +11032,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>C004200910</t>
+          <t>C001759977</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>C004200910 - FERNANDEZ REYES JHENIFER VANESSA</t>
+          <t>C001759977 - ARENAS VARGAS NAOMI STEPHANY</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -10870,7 +11046,7 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -10908,13 +11084,17 @@
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -10946,12 +11126,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>C004180942</t>
+          <t>C001577408</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>C004180942 - ALFARO YUPANQUI EDUAR NILSON</t>
+          <t>C001577408 - CABRERA LOYOLA DIANA MILY</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -10960,7 +11140,7 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -11003,12 +11183,12 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -11040,12 +11220,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>C004060020</t>
+          <t>C001324650</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>C004060020 - GARCIA AURORA SANTOS GILBERTA</t>
+          <t>C001324650 - ULLOA QUEZADA NATIVIDAD VILMA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -11054,7 +11234,7 @@
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -11086,7 +11266,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S117" t="inlineStr"/>
@@ -11097,12 +11277,12 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11134,12 +11314,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>C004183620</t>
+          <t>C001384058</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>C004183620 - RODRIGUEZ TORRES FLORA ARCILA</t>
+          <t>C001384058 - RAMOS ROBLES YANINA BEATRIZ</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -11148,7 +11328,7 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -11180,23 +11360,19 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -11228,12 +11404,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>C004167730</t>
+          <t>C001400565</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>C004167730 - LIZARRAGA BACA FIDELIA AXILDA</t>
+          <t>C001400565 - QUISPE LOZANO SANTOS</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -11242,7 +11418,7 @@
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -11322,12 +11498,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>C004049198</t>
+          <t>C004183506</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>C004049198 - ALFARO YUPANQUI EDUAR NILSON</t>
+          <t>C004183506 - PAREDES VASQUEZ ISABEL NOLBERTA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -11336,7 +11512,7 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -11363,7 +11539,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -11416,12 +11592,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>C001444741</t>
+          <t>C004168628</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>C001444741 - MUNOZ DE PAREDES LUCIA</t>
+          <t>C004168628 - SILVA DOMINGUEZ HERNAN</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -11430,7 +11606,7 @@
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -11468,13 +11644,17 @@
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U121" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11506,12 +11686,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>C004206826</t>
+          <t>C004169388</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>C004206826 - AGREDA RODRIGUEZ MILAGROS DEL PILAR</t>
+          <t>C004169388 - JULCA REYES MARIA ROSMERIA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -11520,7 +11700,7 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -11558,13 +11738,17 @@
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U122" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11596,12 +11780,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>C001521896</t>
+          <t>C004171449</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>C001521896 - VASQUEZ ACOSTA MARIA ROXANI</t>
+          <t>C004171449 - CRUZ QUISPE ETHEL MELIZA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -11610,7 +11794,7 @@
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -11642,19 +11826,23 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U123" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11686,12 +11874,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>C001448981</t>
+          <t>C001740647</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>C001448981 - SANDOVAL CRUZ DE GRADOS DAMIANA</t>
+          <t>C001740647 - SILVA DOMINGUEZ MIRIAM</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -11700,7 +11888,7 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -11780,12 +11968,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>C001674629</t>
+          <t>C001732191</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>C001674629 - VASQUEZ MENDEZ HILDA PALMIRA</t>
+          <t>C001732191 - ZAVALETA CASTAÑEDA OLGA ELOISA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11794,7 +11982,7 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -11811,7 +11999,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
@@ -11874,12 +12066,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>C004240756</t>
+          <t>C001645160</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>C004240756 - ESCOBAL RAMOS MONICA JULISSA</t>
+          <t>C001645160 - GOMEZ UGARTE ROSA</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -11888,7 +12080,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -11968,12 +12160,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>C004241784</t>
+          <t>C004224142</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>C004241784 - RAMOS VALENCIA CONSUELO HAYDEE</t>
+          <t>C004224142 - RAMIREZ FLORES ALEJANDRO DANIEL</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -11982,7 +12174,7 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -12020,13 +12212,17 @@
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U127" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -12058,12 +12254,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>C004060767</t>
+          <t>C001285138</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>C004060767 - VEGA ARGOMEDO LUIS ALBERTO</t>
+          <t>C001285138 - POLO ARANDA DIRSON PAUL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -12072,7 +12268,7 @@
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -12127,7 +12323,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>HUAMACHUCO</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12142,7 +12338,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>Prefiere pedir con su vendedor</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -12152,12 +12348,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>C004167428</t>
+          <t>C001490935</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>C004167428 - RODRIGUEZ CORVERA JAYER LUIS</t>
+          <t>C001490935 - BERROCAL NAPAN JESSICA SOLEDAD</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -12166,7 +12362,7 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -12234,12 +12430,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>C001128320</t>
+          <t>C001521872</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>C001128320 - RODRIGUEZ GARCIA YANIRA EDITH</t>
+          <t>C001521872 - GRAOS BRICENO FREDY RONALD</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -12248,7 +12444,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -12328,12 +12524,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>C001324742</t>
+          <t>C001285463</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>C001324742 - CORTIJO CARRANZA ORTENSIA MARIA</t>
+          <t>C001285463 - DE LA CRUZ ROMAN CLARA</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -12342,7 +12538,7 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -12380,13 +12576,17 @@
       <c r="S131" t="inlineStr"/>
       <c r="T131" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U131" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -12418,12 +12618,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>C001640733</t>
+          <t>C001370989</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>C001640733 - PRETELL CORDOVA EVELYN JANNETH</t>
+          <t>C001370989 - ESQUIVEL ENRIQUEZ TEODOLINDA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -12432,7 +12632,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -12459,7 +12659,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
@@ -12470,20 +12670,24 @@
       <c r="S132" t="inlineStr"/>
       <c r="T132" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U132" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>HUAMACHUCO</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12508,12 +12712,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>C004200980</t>
+          <t>C001455878</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>C004200980 - CHAMBE PADILLA MARIA CIRILA</t>
+          <t>C001455878 - JULCA NEYRA LUIS JAIME</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -12522,7 +12726,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -12602,12 +12806,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>C004242198</t>
+          <t>C001761062</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>C004242198 - ALFARO FLORES MILAGROS AMPARO</t>
+          <t>C001761062 - CERNA PRIETO MARTINA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -12616,7 +12820,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -12696,12 +12900,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>C001767433</t>
+          <t>C004200910</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>C001767433 - RODRIGUEZ BEJARANO SEGUNDO EUSEBIO</t>
+          <t>C004200910 - FERNANDEZ REYES JHENIFER VANESSA</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -12710,7 +12914,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -12748,13 +12952,17 @@
       <c r="S135" t="inlineStr"/>
       <c r="T135" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U135" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -12786,12 +12994,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>C001706144</t>
+          <t>C004183620</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>C001706144 - BARRIOS AGUIRRE NATALI AIME</t>
+          <t>C004183620 - RODRIGUEZ TORRES FLORA ARCILA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -12800,7 +13008,7 @@
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -12880,12 +13088,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>C001568619</t>
+          <t>C004167730</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>C001568619 - GARCIA MENDOZA JORDY JANPIERRE</t>
+          <t>C004167730 - LIZARRAGA BACA FIDELIA AXILDA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -12894,7 +13102,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -12926,19 +13134,23 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S137" t="inlineStr"/>
       <c r="T137" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U137" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -12970,12 +13182,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>C004192601</t>
+          <t>C004060020</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>C004192601 - CARLOS RODRIGUEZ MARLENI LUZVENI</t>
+          <t>C004060020 - GARCIA AURORA SANTOS GILBERTA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -12984,7 +13196,7 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -13016,7 +13228,7 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S138" t="inlineStr"/>
@@ -13027,12 +13239,12 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13276,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>C001634973</t>
+          <t>C004180942</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>C001634973 - FLOREANO ALFARO AUGUSTO ENRIQUE</t>
+          <t>C004180942 - ALFARO YUPANQUI EDUAR NILSON</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -13078,7 +13290,7 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -13116,13 +13328,17 @@
       <c r="S139" t="inlineStr"/>
       <c r="T139" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U139" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -13154,12 +13370,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>C001129172</t>
+          <t>C004049198</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>C001129172 - ROBLES ESPEJO PEDRO</t>
+          <t>C004049198 - ALFARO YUPANQUI EDUAR NILSON</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -13168,7 +13384,7 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -13248,12 +13464,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>C001122173</t>
+          <t>C001444741</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>C001122173 - ESTEBAN POLO MARIA</t>
+          <t>C001444741 - MUNOZ DE PAREDES LUCIA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -13262,7 +13478,7 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -13300,13 +13516,17 @@
       <c r="S141" t="inlineStr"/>
       <c r="T141" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U141" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -13338,12 +13558,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>C001121497</t>
+          <t>C004206826</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>C001121497 - REYES CUEVA ELSA NATALIA</t>
+          <t>C004206826 - AGREDA RODRIGUEZ MILAGROS DEL PILAR</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -13352,7 +13572,7 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -13390,17 +13610,13 @@
       <c r="S142" t="inlineStr"/>
       <c r="T142" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U142" t="inlineStr">
-        <is>
-          <t>Nitro</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -13432,12 +13648,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>C001345662</t>
+          <t>C001521896</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
+          <t>C001521896 - VASQUEZ ACOSTA MARIA ROXANI</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -13446,7 +13662,7 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -13489,12 +13705,12 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -13526,12 +13742,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>C001216214</t>
+          <t>C001448981</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>C001216214 - MALDONADO TRUJILLO DE VILLARREAL ASUNCIO</t>
+          <t>C001448981 - SANDOVAL CRUZ DE GRADOS DAMIANA</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -13540,7 +13756,7 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -13578,18 +13794,1866 @@
       <c r="S144" t="inlineStr"/>
       <c r="T144" t="inlineStr">
         <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>C001640733</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>C001640733 - PRETELL CORDOVA EVELYN JANNETH</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr"/>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>C001674629</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>C001674629 - VASQUEZ MENDEZ HILDA PALMIRA</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Otros Motivos</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>C004167428</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>C004167428 - RODRIGUEZ CORVERA JAYER LUIS</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr"/>
-      <c r="V144" t="inlineStr">
+      <c r="I147" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>No Efectivo</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>SI - Solo tiene pedido por Nitro</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>C004060767</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>C004060767 - VEGA ARGOMEDO LUIS ALBERTO</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr"/>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>C004240756</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>C004240756 - ESCOBAL RAMOS MONICA JULISSA</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr"/>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>C004241784</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>C004241784 - RAMOS VALENCIA CONSUELO HAYDEE</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr"/>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>SI - Solo tiene pedido por Nitro</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>C001128320</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>C001128320 - RODRIGUEZ GARCIA YANIRA EDITH</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr"/>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>C001324742</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>C001324742 - CORTIJO CARRANZA ORTENSIA MARIA</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr"/>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr">
         <is>
           <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>C004242198</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>C004242198 - ALFARO FLORES MILAGROS AMPARO</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr"/>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>C004200980</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>C004200980 - CHAMBE PADILLA MARIA CIRILA</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr"/>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>C001767433</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>C001767433 - RODRIGUEZ BEJARANO SEGUNDO EUSEBIO</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr"/>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>NO - No hizo pedido</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>C001706144</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>C001706144 - BARRIOS AGUIRRE NATALI AIME</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr"/>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>C004192601</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>C004192601 - CARLOS RODRIGUEZ MARLENI LUZVENI</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>C001345662</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr"/>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>C001216214</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>C001216214 - MALDONADO TRUJILLO DE VILLARREAL ASUNCIO</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr"/>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>NO - No hizo pedido</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>C001129172</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>C001129172 - ROBLES ESPEJO PEDRO</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr"/>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>C001122173</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>C001122173 - ESTEBAN POLO MARIA</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr"/>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>NO - No hizo pedido</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>C001121497</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>C001121497 - REYES CUEVA ELSA NATALIA</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr"/>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SI - Solo tiene pedido por Nitro</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>C001634973</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>C001634973 - FLOREANO ALFARO AUGUSTO ENRIQUE</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr"/>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>NO - No hizo pedido</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1000054785</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA SOL DEL VALLE S.A.C.</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>GIL MELGAREJO, OSCAR FERNANDO JUNIOR</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>C001568619</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>C001568619 - GARCIA MENDOZA JORDY JANPIERRE</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Efectivo</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>Más confianza en la entrega</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr"/>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>NO - No hizo pedido</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V144"/>
+  <autoFilter ref="A1:V164"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/excel/distribuidora-sol-del-valle-s-a-c_capacitaciones.xlsx
+++ b/excel/distribuidora-sol-del-valle-s-a-c_capacitaciones.xlsx
@@ -598,12 +598,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C001345662</t>
+          <t>C001396749</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
+          <t>C001396749 - FLORES ROSALES JUANITA JULIA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -650,17 +650,13 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -672,7 +668,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -692,12 +688,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C001405781</t>
+          <t>C001398311</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>C001405781 - ARAUJO AGUILAR KELLER MARJORIE</t>
+          <t>C001398311 - ARAUJO QUILICHE ANA CLAIRE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -782,12 +778,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C001396749</t>
+          <t>C001345662</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C001396749 - FLORES ROSALES JUANITA JULIA</t>
+          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -834,13 +830,17 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C001398311</t>
+          <t>C001405781</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>C001398311 - ARAUJO QUILICHE ANA CLAIRE</t>
+          <t>C001405781 - ARAUJO AGUILAR KELLER MARJORIE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C001612867</t>
+          <t>C001767433</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C001612867 - DIAZ RAFAEL ERIKA MARIVI</t>
+          <t>C001767433 - RODRIGUEZ BEJARANO SEGUNDO EUSEBIO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Más capacitación</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S6" t="inlineStr"/>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C001767433</t>
+          <t>C001626791</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C001767433 - RODRIGUEZ BEJARANO SEGUNDO EUSEBIO</t>
+          <t>C001626791 - RAMIREZ BERNABE JEAN POOL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C001626791</t>
+          <t>C001612867</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>C001626791 - RAMIREZ BERNABE JEAN POOL</t>
+          <t>C001612867 - DIAZ RAFAEL ERIKA MARIVI</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Más capacitación</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C004192601</t>
+          <t>C004242198</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>C004192601 - CARLOS RODRIGUEZ MARLENI LUZVENI</t>
+          <t>C004242198 - ALFARO FLORES MILAGROS AMPARO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1268,7 +1268,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C004050172</t>
+          <t>C004192601</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C004050172 - RODRIGUEZ VASQUEZ ROSARIO ANGELICA</t>
+          <t>C004192601 - CARLOS RODRIGUEZ MARLENI LUZVENI</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1468,13 +1468,17 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1510,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C004167425</t>
+          <t>C004050172</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>C004167425 - FELIPE BAZAN DE ROJAS BETTY MARUJA</t>
+          <t>C004050172 - RODRIGUEZ VASQUEZ ROSARIO ANGELICA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1558,17 +1562,13 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C004242198</t>
+          <t>C004167425</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>C004242198 - ALFARO FLORES MILAGROS AMPARO</t>
+          <t>C004167425 - FELIPE BAZAN DE ROJAS BETTY MARUJA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1636,7 +1636,7 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C001364499</t>
+          <t>C001409233</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C001364499 - BURGOS DE QUISPE OLGA DALILA</t>
+          <t>C001409233 - VERA CRUZ NATHALY SAMANTHA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C001559213</t>
+          <t>C001364499</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C001559213 - RUIZ ESPINOZA DELIA ISABEL</t>
+          <t>C001364499 - BURGOS DE QUISPE OLGA DALILA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1920,23 +1920,19 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -1968,12 +1964,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C001676127</t>
+          <t>C001559213</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>C001676127 - ESCOVEDO AREDO ANITA ANDREA</t>
+          <t>C001559213 - RUIZ ESPINOZA DELIA ISABEL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2020,13 +2016,17 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C004190849</t>
+          <t>C001676127</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C004190849 - VALVERDE ULLOA SANTOS AGUSTINA</t>
+          <t>C001676127 - ESCOVEDO AREDO ANITA ANDREA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2089,11 +2089,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2132,7 +2128,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2152,12 +2148,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C001409233</t>
+          <t>C004190849</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>C001409233 - VERA CRUZ NATHALY SAMANTHA</t>
+          <t>C004190849 - VALVERDE ULLOA SANTOS AGUSTINA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2183,7 +2179,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C001572723</t>
+          <t>C001562946</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C001572723 - LIÑAN TORRES ASUNCION ROSMERY</t>
+          <t>C001562946 - CUSTODIO BRICEÑO LILY MARILU</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2288,23 +2288,19 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2332,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C001562946</t>
+          <t>C001572723</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>C001562946 - CUSTODIO BRICEÑO LILY MARILU</t>
+          <t>C001572723 - LIÑAN TORRES ASUNCION ROSMERY</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2382,19 +2378,23 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C001674351</t>
+          <t>C001669043</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>C001674351 - YSIDRO SOCORRO ANELIDA</t>
+          <t>C001669043 - ORBEGOSO MUÑOZ EMELDA ELIZABETH</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>C001669043</t>
+          <t>C001674351</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>C001669043 - ORBEGOSO MUÑOZ EMELDA ELIZABETH</t>
+          <t>C001674351 - YSIDRO SOCORRO ANELIDA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>C001483227</t>
+          <t>C001513040</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>C001483227 - VILLANUEVA HILARIO CYNTHIA YESENIA</t>
+          <t>C001513040 - ACOSTA FERNANDEZ MARCELINA ESTHER</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>C001513040</t>
+          <t>C001483227</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>C001513040 - ACOSTA FERNANDEZ MARCELINA ESTHER</t>
+          <t>C001483227 - VILLANUEVA HILARIO CYNTHIA YESENIA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
@@ -3620,12 +3620,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C001760417</t>
+          <t>C004048840</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>C001760417 - BOCANEGRA HILARIO JHOORDYN AQUILES</t>
+          <t>C004048840 - CORTIJO NEYRA LUCERO DEL CIELO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3656,7 +3656,7 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Algo dispuesto</t>
+          <t>Muy dispuesto</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3666,19 +3666,23 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Apoyo del vendedor</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3714,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>C004048840</t>
+          <t>C001760417</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>C004048840 - CORTIJO NEYRA LUCERO DEL CIELO</t>
+          <t>C001760417 - BOCANEGRA HILARIO JHOORDYN AQUILES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3746,7 +3750,7 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Muy dispuesto</t>
+          <t>Algo dispuesto</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3756,23 +3760,19 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Apoyo del vendedor</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>C004199228</t>
+          <t>C004190467</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>C004199228 - VALDIVIESO CABRERA VICTOR MELITON</t>
+          <t>C004190467 - GARCIA FAJARDO JAMPOOL JUNIOR</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
@@ -3898,12 +3898,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C004190467</t>
+          <t>C004199228</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>C004190467 - GARCIA FAJARDO JAMPOOL JUNIOR</t>
+          <t>C004199228 - VALDIVIESO CABRERA VICTOR MELITON</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C001711464</t>
+          <t>C004054693</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>C001711464 - DIONICIO HERNANDEZ MIRTA</t>
+          <t>C004054693 - VASQUEZ VALDERRAMA SARA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C001740965</t>
+          <t>C004059726</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>C001740965 - LAZARO NICASIO MARIBEL KARINA</t>
+          <t>C004059726 - GERONIMO PEREZ MARINO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4117,11 +4117,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -4180,12 +4176,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C004054693</t>
+          <t>C001711464</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>C004054693 - VASQUEZ VALDERRAMA SARA</t>
+          <t>C001711464 - DIONICIO HERNANDEZ MIRTA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4254,7 +4250,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4274,12 +4270,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C004059726</t>
+          <t>C001740965</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>C004059726 - GERONIMO PEREZ MARINO</t>
+          <t>C001740965 - LAZARO NICASIO MARIBEL KARINA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4305,7 +4301,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -4364,12 +4364,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>C001629991</t>
+          <t>C001563276</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>C001629991 - AVILA RODRIGUEZ LADY ROSSELLI</t>
+          <t>C001563276 - MENDEZ MENDEZ DEROMILDA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C001618305</t>
+          <t>C001576999</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>C001618305 - MOGOLLON GARCIA JORGE LUIS</t>
+          <t>C001576999 - TORRES LIZARRAGA GIANMARCO ANDRE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4510,13 +4510,17 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Nitro</t>
+        </is>
+      </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4532,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4548,12 +4552,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>C001563276</t>
+          <t>C001618305</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>C001563276 - MENDEZ MENDEZ DEROMILDA</t>
+          <t>C001618305 - MOGOLLON GARCIA JORGE LUIS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4594,23 +4598,19 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>C001576999</t>
+          <t>C001629991</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>C001576999 - TORRES LIZARRAGA GIANMARCO ANDRE</t>
+          <t>C001629991 - AVILA RODRIGUEZ LADY ROSSELLI</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S46" t="inlineStr"/>
@@ -4699,12 +4699,12 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -4736,12 +4736,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C001405766</t>
+          <t>C001392282</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>C001405766 - CASTAÑEDA CASTAÑEDA EMILIO</t>
+          <t>C001392282 - POLO CRUZ JOSE SANTOS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C001392282</t>
+          <t>C001405766</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>C001392282 - POLO CRUZ JOSE SANTOS</t>
+          <t>C001405766 - CASTAÑEDA CASTAÑEDA EMILIO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1000054782</t>
+          <t>1000054785</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5010,12 +5010,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C001731317</t>
+          <t>C001712645</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>C001731317 - SANCHEZ MOZO MILI YOVANA</t>
+          <t>C001712645 - GUTIERREZ ROJAS ELVIN</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C001734971</t>
+          <t>C001513253</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>C001734971 - ALVARADO PRADO PEDRO NILTON</t>
+          <t>C001513253 - RODRIGUEZ VALDIVIESO YULI DEYSI</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1000054785</t>
+          <t>1000054782</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C001513253</t>
+          <t>C001731317</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>C001513253 - RODRIGUEZ VALDIVIESO YULI DEYSI</t>
+          <t>C001731317 - SANCHEZ MOZO MILI YOVANA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C001712645</t>
+          <t>C001734971</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>C001712645 - GUTIERREZ ROJAS ELVIN</t>
+          <t>C001734971 - ALVARADO PRADO PEDRO NILTON</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C004170116</t>
+          <t>C001332822</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>C004170116 - REYES SALINAS MARTHA PEREGRINA</t>
+          <t>C001332822 - PINILLOS MARCELO KAREN TATIANA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5422,13 +5422,17 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -5460,12 +5464,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C001741503</t>
+          <t>C004170116</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>C001741503 - FERREL DIESTRA ALEJANDRINA TEONILA</t>
+          <t>C004170116 - REYES SALINAS MARTHA PEREGRINA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5501,7 +5505,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5730,12 +5734,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C001332822</t>
+          <t>C001741503</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>C001332822 - PINILLOS MARCELO KAREN TATIANA</t>
+          <t>C001741503 - FERREL DIESTRA ALEJANDRINA TEONILA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5771,7 +5775,7 @@
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5782,17 +5786,13 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -5824,12 +5824,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C004242893</t>
+          <t>C004170162</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>C004242893 - MULTISERVICIOS GENERALES ZAVALETA S.A.C.</t>
+          <t>C004170162 - RODRIGUEZ RUIZ ADRIANA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
@@ -5914,12 +5914,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C004170162</t>
+          <t>C004242893</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>C004170162 - RODRIGUEZ RUIZ ADRIANA</t>
+          <t>C004242893 - MULTISERVICIOS GENERALES ZAVALETA S.A.C.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S60" t="inlineStr"/>
@@ -6004,12 +6004,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C001682053</t>
+          <t>C001733600</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>C001682053 - CONTRERAS MARQUINA IDAÑA MARDELID</t>
+          <t>C001733600 - REYES CABRERA MELBER AGAPITO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6035,7 +6035,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
@@ -6098,12 +6102,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>C001667496</t>
+          <t>C001731770</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>C001667496 - RODRIGUEZ AGUILAR FLORA</t>
+          <t>C001731770 - BENITEZ RODRIGUEZ SEGUNDA FLORESTINA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6192,12 +6196,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>C001529571</t>
+          <t>C001682053</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>C001529571 - CRUZADO PULIDO LORENA LICETH</t>
+          <t>C001682053 - CONTRERAS MARQUINA IDAÑA MARDELID</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -6244,13 +6248,17 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -6282,12 +6290,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>C001476009</t>
+          <t>C001667496</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>C001476009 - JARA VILLAR ADOLFINA PETRONILA</t>
+          <t>C001667496 - RODRIGUEZ AGUILAR FLORA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -6376,12 +6384,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>C001733600</t>
+          <t>C001529571</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>C001733600 - REYES CABRERA MELBER AGAPITO</t>
+          <t>C001529571 - CRUZADO PULIDO LORENA LICETH</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -6407,11 +6415,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -6432,17 +6436,13 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -6474,12 +6474,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>C001731770</t>
+          <t>C001476009</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>C001731770 - BENITEZ RODRIGUEZ SEGUNDA FLORESTINA</t>
+          <t>C001476009 - JARA VILLAR ADOLFINA PETRONILA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>C001127634</t>
+          <t>C004166670</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>C001127634 - VIDAL GARCIA TERESA</t>
+          <t>C004166670 - RODRIGUEZ RODRIGUEZ GABBY ROSSI</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -8976,12 +8976,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>C001128962</t>
+          <t>C001567587</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>C001128962 - PAREDES HUAMAN SANTOS PETRONILA</t>
+          <t>C001567587 - RUIZ MIÑANO ROSA FLOR</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -9033,12 +9033,12 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9070,12 +9070,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>C004166670</t>
+          <t>C001578039</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>C004166670 - RODRIGUEZ RODRIGUEZ GABBY ROSSI</t>
+          <t>C001578039 - AGUILAR URRUTIA ROSA KELLY</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -9164,12 +9164,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>C001578039</t>
+          <t>C001401840</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>C001578039 - AGUILAR URRUTIA ROSA KELLY</t>
+          <t>C001401840 - VILLARREAL CONTRERAS ANACLETO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -9258,12 +9258,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>C001567587</t>
+          <t>C001324442</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>C001567587 - RUIZ MIÑANO ROSA FLOR</t>
+          <t>C001324442 - GUTIERREZ DE OTINIANO SANTOS NILA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9310,17 +9310,13 @@
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -9352,12 +9348,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>C001401840</t>
+          <t>C001127634</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>C001401840 - VILLARREAL CONTRERAS ANACLETO</t>
+          <t>C001127634 - VIDAL GARCIA TERESA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9446,12 +9442,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C001367258</t>
+          <t>C001128962</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>C001367258 - JOAQUIN SOBERON EDITH</t>
+          <t>C001128962 - PAREDES HUAMAN SANTOS PETRONILA</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -9487,7 +9483,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -9503,12 +9499,12 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -9540,12 +9536,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>C001324442</t>
+          <t>C001367258</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>C001324442 - GUTIERREZ DE OTINIANO SANTOS NILA</t>
+          <t>C001367258 - JOAQUIN SOBERON EDITH</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -9581,7 +9577,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -9592,13 +9588,17 @@
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11126,12 +11126,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>C001577408</t>
+          <t>C004183506</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>C001577408 - CABRERA LOYOLA DIANA MILY</t>
+          <t>C004183506 - PAREDES VASQUEZ ISABEL NOLBERTA</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>Buscar productos</t>
+          <t>Iniciar sesión</t>
         </is>
       </c>
       <c r="R116" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11220,12 +11220,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>C001324650</t>
+          <t>C001384058</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>C001324650 - ULLOA QUEZADA NATIVIDAD VILMA</t>
+          <t>C001384058 - RAMOS ROBLES YANINA BEATRIZ</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -11272,17 +11272,13 @@
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -11314,12 +11310,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>C001384058</t>
+          <t>C001400565</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>C001384058 - RAMOS ROBLES YANINA BEATRIZ</t>
+          <t>C001400565 - QUISPE LOZANO SANTOS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -11360,19 +11356,23 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U118" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -11404,12 +11404,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>C001400565</t>
+          <t>C001324650</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>C001400565 - QUISPE LOZANO SANTOS</t>
+          <t>C001324650 - ULLOA QUEZADA NATIVIDAD VILMA</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S119" t="inlineStr"/>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>C004183506</t>
+          <t>C001577408</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>C004183506 - PAREDES VASQUEZ ISABEL NOLBERTA</t>
+          <t>C001577408 - CABRERA LOYOLA DIANA MILY</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>Iniciar sesión</t>
+          <t>Buscar productos</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
@@ -11555,12 +11555,12 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>C001740647</t>
+          <t>C001645160</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>C001740647 - SILVA DOMINGUEZ MIRIAM</t>
+          <t>C001645160 - GOMEZ UGARTE ROSA</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>C001732191</t>
+          <t>C001740647</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>C001732191 - ZAVALETA CASTAÑEDA OLGA ELOISA</t>
+          <t>C001740647 - SILVA DOMINGUEZ MIRIAM</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -11999,11 +11999,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
@@ -12066,12 +12062,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>C001645160</t>
+          <t>C001732191</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>C001645160 - GOMEZ UGARTE ROSA</t>
+          <t>C001732191 - ZAVALETA CASTAÑEDA OLGA ELOISA</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -12097,7 +12093,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
@@ -12499,7 +12499,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TRUJILLO</t>
+          <t>HUAMACHUCO</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>C001285463</t>
+          <t>C001455878</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>C001285463 - DE LA CRUZ ROMAN CLARA</t>
+          <t>C001455878 - JULCA NEYRA LUIS JAIME</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -12581,12 +12581,12 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -12687,7 +12687,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>HUAMACHUCO</t>
+          <t>TRUJILLO</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>C001455878</t>
+          <t>C001285463</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>C001455878 - JULCA NEYRA LUIS JAIME</t>
+          <t>C001285463 - DE LA CRUZ ROMAN CLARA</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -12994,12 +12994,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>C004183620</t>
+          <t>C004180942</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>C004183620 - RODRIGUEZ TORRES FLORA ARCILA</t>
+          <t>C004180942 - ALFARO YUPANQUI EDUAR NILSON</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -13088,12 +13088,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>C004167730</t>
+          <t>C004183620</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>C004167730 - LIZARRAGA BACA FIDELIA AXILDA</t>
+          <t>C004183620 - RODRIGUEZ TORRES FLORA ARCILA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -13182,12 +13182,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>C004060020</t>
+          <t>C004167730</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>C004060020 - GARCIA AURORA SANTOS GILBERTA</t>
+          <t>C004167730 - LIZARRAGA BACA FIDELIA AXILDA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -13239,12 +13239,12 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -13276,12 +13276,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>C004180942</t>
+          <t>C004060020</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>C004180942 - ALFARO YUPANQUI EDUAR NILSON</t>
+          <t>C004060020 - GARCIA AURORA SANTOS GILBERTA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -13333,12 +13333,12 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -13648,12 +13648,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>C001521896</t>
+          <t>C001448981</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>C001521896 - VASQUEZ ACOSTA MARIA ROXANI</t>
+          <t>C001448981 - SANDOVAL CRUZ DE GRADOS DAMIANA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -13742,12 +13742,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>C001448981</t>
+          <t>C001521896</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>C001448981 - SANDOVAL CRUZ DE GRADOS DAMIANA</t>
+          <t>C001521896 - VASQUEZ ACOSTA MARIA ROXANI</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -13799,12 +13799,12 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -13836,12 +13836,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>C001640733</t>
+          <t>C001674629</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>C001640733 - PRETELL CORDOVA EVELYN JANNETH</t>
+          <t>C001674629 - VASQUEZ MENDEZ HILDA PALMIRA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>C001674629</t>
+          <t>C004240756</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>C001674629 - VASQUEZ MENDEZ HILDA PALMIRA</t>
+          <t>C004240756 - ESCOBAL RAMOS MONICA JULISSA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Otros Motivos</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -14024,17 +14024,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>C004167428</t>
+          <t>C004241784</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>C004167428 - RODRIGUEZ CORVERA JAYER LUIS</t>
+          <t>C004241784 - RAMOS VALENCIA CONSUELO HAYDEE</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>No Efectivo</t>
+          <t>Efectivo</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -14058,9 +14058,21 @@
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr"/>
-      <c r="R147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Muy dispuesto</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Buscar productos</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Mejores promociones</t>
+        </is>
+      </c>
       <c r="S147" t="inlineStr"/>
       <c r="T147" t="inlineStr">
         <is>
@@ -14190,7 +14202,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Otros Motivos</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -14200,17 +14212,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>C004240756</t>
+          <t>C004167428</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>C004240756 - ESCOBAL RAMOS MONICA JULISSA</t>
+          <t>C004167428 - RODRIGUEZ CORVERA JAYER LUIS</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
@@ -14223,7 +14235,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Efectivo</t>
+          <t>No Efectivo</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -14234,21 +14246,9 @@
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>Muy dispuesto</t>
-        </is>
-      </c>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>Buscar productos</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>Mejores promociones</t>
-        </is>
-      </c>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr"/>
       <c r="T149" t="inlineStr">
         <is>
@@ -14257,12 +14257,12 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>Cliente</t>
+          <t>Nitro</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>SI - Solo tiene pedido por Nitro</t>
         </is>
       </c>
     </row>
@@ -14294,12 +14294,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>C004241784</t>
+          <t>C001128320</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>C004241784 - RAMOS VALENCIA CONSUELO HAYDEE</t>
+          <t>C001128320 - RODRIGUEZ GARCIA YANIRA EDITH</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -14351,12 +14351,12 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>Nitro</t>
+          <t>Cliente</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
         <is>
-          <t>SI - Solo tiene pedido por Nitro</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>C001128320</t>
+          <t>C001324742</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>C001128320 - RODRIGUEZ GARCIA YANIRA EDITH</t>
+          <t>C001324742 - CORTIJO CARRANZA ORTENSIA MARIA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -14440,17 +14440,13 @@
       <c r="S151" t="inlineStr"/>
       <c r="T151" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr"/>
       <c r="V151" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -14482,12 +14478,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>C001324742</t>
+          <t>C001640733</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>C001324742 - CORTIJO CARRANZA ORTENSIA MARIA</t>
+          <t>C001640733 - PRETELL CORDOVA EVELYN JANNETH</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -14534,13 +14530,17 @@
       <c r="S152" t="inlineStr"/>
       <c r="T152" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U152" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V152" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -14572,12 +14572,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>C004242198</t>
+          <t>C004200980</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>C004242198 - ALFARO FLORES MILAGROS AMPARO</t>
+          <t>C004200980 - CHAMBE PADILLA MARIA CIRILA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -14666,12 +14666,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>C004200980</t>
+          <t>C004242198</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>C004200980 - CHAMBE PADILLA MARIA CIRILA</t>
+          <t>C004242198 - ALFARO FLORES MILAGROS AMPARO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -14944,12 +14944,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>C004192601</t>
+          <t>C001568619</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>C004192601 - CARLOS RODRIGUEZ MARLENI LUZVENI</t>
+          <t>C001568619 - GARCIA MENDOZA JORDY JANPIERRE</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -14996,17 +14996,13 @@
       <c r="S157" t="inlineStr"/>
       <c r="T157" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="U157" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr"/>
       <c r="V157" t="inlineStr">
         <is>
-          <t>SI - Cliente hizo pedido (autogestionado)</t>
+          <t>NO - No hizo pedido</t>
         </is>
       </c>
     </row>
@@ -15038,12 +15034,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>C001345662</t>
+          <t>C004192601</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
+          <t>C004192601 - CARLOS RODRIGUEZ MARLENI LUZVENI</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -15084,7 +15080,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>Mejores promociones</t>
+          <t>Más confianza en la entrega</t>
         </is>
       </c>
       <c r="S158" t="inlineStr"/>
@@ -15132,12 +15128,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>C001216214</t>
+          <t>C001634973</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>C001216214 - MALDONADO TRUJILLO DE VILLARREAL ASUNCIO</t>
+          <t>C001634973 - FLOREANO ALFARO AUGUSTO ENRIQUE</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -15500,12 +15496,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>C001634973</t>
+          <t>C001345662</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>C001634973 - FLOREANO ALFARO AUGUSTO ENRIQUE</t>
+          <t>C001345662 - MAURICIO DE LA CRUZ EUGENIA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -15552,13 +15548,17 @@
       <c r="S163" t="inlineStr"/>
       <c r="T163" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="U163" t="inlineStr"/>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
       <c r="V163" t="inlineStr">
         <is>
-          <t>NO - No hizo pedido</t>
+          <t>SI - Cliente hizo pedido (autogestionado)</t>
         </is>
       </c>
     </row>
@@ -15590,12 +15590,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>C001568619</t>
+          <t>C001216214</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>C001568619 - GARCIA MENDOZA JORDY JANPIERRE</t>
+          <t>C001216214 - MALDONADO TRUJILLO DE VILLARREAL ASUNCIO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -15636,7 +15636,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Más confianza en la entrega</t>
+          <t>Mejores promociones</t>
         </is>
       </c>
       <c r="S164" t="inlineStr"/>
